--- a/nr-init/ig/all-profiles.xlsx
+++ b/nr-init/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:22:06+00:00</t>
+    <t>2025-03-14T15:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/all-profiles.xlsx
+++ b/nr-init/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:23:56+00:00</t>
+    <t>2025-03-14T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
